--- a/data/xlsx/ADANDOGOU Afiwa Pamela  PAS TERMINE.xlsx
+++ b/data/xlsx/ADANDOGOU Afiwa Pamela  PAS TERMINE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROJET_ATLAS_MASTER\atlas\data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E52C84D5-842A-439E-A597-7069D8783421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800ACE65-4B6D-43FE-BD92-D416068955EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="23" activeTab="23" xr2:uid="{BCDE39AB-4EE5-4B44-A173-75C97F1C8DFD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="22" activeTab="25" xr2:uid="{BCDE39AB-4EE5-4B44-A173-75C97F1C8DFD}"/>
   </bookViews>
   <sheets>
     <sheet name="AGTAssahoum" sheetId="1" r:id="rId1"/>
@@ -49,12 +49,22 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="160">
   <si>
     <t>Taleau3-3:Analyse granulométriquepar timisage    et  sédimentometrie   de l'argile</t>
   </si>
@@ -222,6 +232,318 @@
   </si>
   <si>
     <t xml:space="preserve">Tableau A-6: Analyse granulométrie par tamisage </t>
+  </si>
+  <si>
+    <t>Ouverture du tamis (mm)</t>
+  </si>
+  <si>
+    <t>Masse de refus cumulés (g)</t>
+  </si>
+  <si>
+    <t>Refus cumulés (%)</t>
+  </si>
+  <si>
+    <t>Passants (%)</t>
+  </si>
+  <si>
+    <t>Analyse granulométrique par tamisage</t>
+  </si>
+  <si>
+    <t>0,00</t>
+  </si>
+  <si>
+    <t>100,00</t>
+  </si>
+  <si>
+    <t>10,20</t>
+  </si>
+  <si>
+    <t>0,37</t>
+  </si>
+  <si>
+    <t>99,63</t>
+  </si>
+  <si>
+    <t>6,3</t>
+  </si>
+  <si>
+    <t>15,00</t>
+  </si>
+  <si>
+    <t>0,55</t>
+  </si>
+  <si>
+    <t>99,45</t>
+  </si>
+  <si>
+    <t>22,10</t>
+  </si>
+  <si>
+    <t>0,81</t>
+  </si>
+  <si>
+    <t>99,19</t>
+  </si>
+  <si>
+    <t>32,80</t>
+  </si>
+  <si>
+    <t>1,19</t>
+  </si>
+  <si>
+    <t>98,81</t>
+  </si>
+  <si>
+    <t>3,15</t>
+  </si>
+  <si>
+    <t>48,10</t>
+  </si>
+  <si>
+    <t>1,75</t>
+  </si>
+  <si>
+    <t>98,25</t>
+  </si>
+  <si>
+    <t>2,5</t>
+  </si>
+  <si>
+    <t>76,80</t>
+  </si>
+  <si>
+    <t>2,80</t>
+  </si>
+  <si>
+    <t>97,20</t>
+  </si>
+  <si>
+    <t>111,40</t>
+  </si>
+  <si>
+    <t>4,06</t>
+  </si>
+  <si>
+    <t>95,94</t>
+  </si>
+  <si>
+    <t>1,6</t>
+  </si>
+  <si>
+    <t>166,90</t>
+  </si>
+  <si>
+    <t>6,08</t>
+  </si>
+  <si>
+    <t>93,92</t>
+  </si>
+  <si>
+    <t>1,25</t>
+  </si>
+  <si>
+    <t>236,20</t>
+  </si>
+  <si>
+    <t>8,60</t>
+  </si>
+  <si>
+    <t>91,40</t>
+  </si>
+  <si>
+    <t>323,20</t>
+  </si>
+  <si>
+    <t>11,77</t>
+  </si>
+  <si>
+    <t>88,23</t>
+  </si>
+  <si>
+    <t>0,8</t>
+  </si>
+  <si>
+    <t>420,30</t>
+  </si>
+  <si>
+    <t>15,31</t>
+  </si>
+  <si>
+    <t>84,69</t>
+  </si>
+  <si>
+    <t>0,63</t>
+  </si>
+  <si>
+    <t>551,40</t>
+  </si>
+  <si>
+    <t>20,09</t>
+  </si>
+  <si>
+    <t>79,91</t>
+  </si>
+  <si>
+    <t>0,5</t>
+  </si>
+  <si>
+    <t>667,70</t>
+  </si>
+  <si>
+    <t>24,32</t>
+  </si>
+  <si>
+    <t>75,68</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>760,30</t>
+  </si>
+  <si>
+    <t>27,70</t>
+  </si>
+  <si>
+    <t>72,30</t>
+  </si>
+  <si>
+    <t>0,315</t>
+  </si>
+  <si>
+    <t>873,50</t>
+  </si>
+  <si>
+    <t>31,82</t>
+  </si>
+  <si>
+    <t>68,18</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>959,70</t>
+  </si>
+  <si>
+    <t>34,96</t>
+  </si>
+  <si>
+    <t>65,04</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>1116,40</t>
+  </si>
+  <si>
+    <t>40,67</t>
+  </si>
+  <si>
+    <t>59,33</t>
+  </si>
+  <si>
+    <t>0,16</t>
+  </si>
+  <si>
+    <t>1271,00</t>
+  </si>
+  <si>
+    <t>46,30</t>
+  </si>
+  <si>
+    <t>53,70</t>
+  </si>
+  <si>
+    <t>0,125</t>
+  </si>
+  <si>
+    <t>1341,80</t>
+  </si>
+  <si>
+    <t>48,88</t>
+  </si>
+  <si>
+    <t>51,12</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>1376,50</t>
+  </si>
+  <si>
+    <t>50,15</t>
+  </si>
+  <si>
+    <t>49,85</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>1412,70</t>
+  </si>
+  <si>
+    <t>51,46</t>
+  </si>
+  <si>
+    <t>48,54</t>
+  </si>
+  <si>
+    <t>Analyse granulométrique par sédimentométrie</t>
+  </si>
+  <si>
+    <t>0,0671</t>
+  </si>
+  <si>
+    <t>38,94</t>
+  </si>
+  <si>
+    <t>0,0474</t>
+  </si>
+  <si>
+    <t>31,70</t>
+  </si>
+  <si>
+    <t>0,0331</t>
+  </si>
+  <si>
+    <t>30,59</t>
+  </si>
+  <si>
+    <t>0,0211</t>
+  </si>
+  <si>
+    <t>29,48</t>
+  </si>
+  <si>
+    <t>0,0150</t>
+  </si>
+  <si>
+    <t>26,71</t>
+  </si>
+  <si>
+    <t>0,0108</t>
+  </si>
+  <si>
+    <t>24,48</t>
+  </si>
+  <si>
+    <t>0,0077</t>
+  </si>
+  <si>
+    <t>22,81</t>
+  </si>
+  <si>
+    <t>0,0055</t>
+  </si>
+  <si>
+    <t>21,10</t>
+  </si>
+  <si>
+    <t>0,0032</t>
   </si>
 </sst>
 </file>
@@ -580,21 +902,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797E9B4D-63E2-496E-8E2F-77B4D381C0CC}">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>1</v>
       </c>
@@ -608,7 +930,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>25</v>
       </c>
@@ -622,7 +944,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>20</v>
       </c>
@@ -636,7 +958,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>100</v>
       </c>
@@ -647,7 +969,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>12.5</v>
       </c>
@@ -661,7 +983,7 @@
         <v>99.33</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -678,7 +1000,7 @@
         <v>98.09</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>8</v>
       </c>
@@ -692,7 +1014,7 @@
         <v>95.85</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>6.3</v>
       </c>
@@ -706,7 +1028,7 @@
         <v>91.58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>5</v>
       </c>
@@ -720,7 +1042,7 @@
         <v>74.010000000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>4</v>
       </c>
@@ -734,7 +1056,7 @@
         <v>65.849999999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>3.15</v>
       </c>
@@ -748,7 +1070,7 @@
         <v>57.61</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>2.5</v>
       </c>
@@ -762,7 +1084,7 @@
         <v>49.53</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>2</v>
       </c>
@@ -776,7 +1098,7 @@
         <v>45.74</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>1.6</v>
       </c>
@@ -790,7 +1112,7 @@
         <v>43.65</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>1.25</v>
       </c>
@@ -804,7 +1126,7 @@
         <v>41.93</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>1</v>
       </c>
@@ -818,7 +1140,7 @@
         <v>40.08</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>0.8</v>
       </c>
@@ -832,7 +1154,7 @@
         <v>38.270000000000003</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>0.63</v>
       </c>
@@ -846,7 +1168,7 @@
         <v>36.200000000000003</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>0.5</v>
       </c>
@@ -860,7 +1182,7 @@
         <v>33.909999999999997</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>0.4</v>
       </c>
@@ -874,7 +1196,7 @@
         <v>31.89</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>0.315</v>
       </c>
@@ -888,7 +1210,7 @@
         <v>29.81</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>0.25</v>
       </c>
@@ -902,7 +1224,7 @@
         <v>28.81</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>0.2</v>
       </c>
@@ -916,7 +1238,7 @@
         <v>26.47</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>0.16</v>
       </c>
@@ -930,7 +1252,7 @@
         <v>24.92</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30">
         <v>0.125</v>
       </c>
@@ -944,7 +1266,7 @@
         <v>24.33</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>0.1</v>
       </c>
@@ -958,7 +1280,7 @@
         <v>24.08</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32">
         <v>0.08</v>
       </c>
@@ -980,24 +1302,24 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{577BE677-9669-44C4-B52E-30A7A57FF6F0}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="60.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="1"/>
-    <col min="3" max="3" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="1"/>
-    <col min="5" max="5" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.5546875" style="1"/>
-    <col min="8" max="8" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="60.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" style="1"/>
+    <col min="3" max="3" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" style="1"/>
+    <col min="5" max="5" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.5703125" style="1"/>
+    <col min="8" max="8" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1020,7 +1342,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -1043,7 +1365,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -1066,7 +1388,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>1</v>
       </c>
@@ -1089,7 +1411,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>1</v>
       </c>
@@ -1112,7 +1434,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>2</v>
       </c>
@@ -1135,7 +1457,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>2</v>
       </c>
@@ -1158,7 +1480,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>2</v>
       </c>
@@ -1181,7 +1503,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>2</v>
       </c>
@@ -1204,7 +1526,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>3</v>
       </c>
@@ -1227,7 +1549,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>3</v>
       </c>
@@ -1250,7 +1572,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>3</v>
       </c>
@@ -1273,7 +1595,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>3</v>
       </c>
@@ -1304,23 +1626,23 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D684E5F-D7EB-4869-8B05-D0E05C46EF01}">
   <dimension ref="A2:F12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="2"/>
-    <col min="2" max="2" width="16.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="2"/>
+    <col min="1" max="1" width="11.5703125" style="2"/>
+    <col min="2" max="2" width="16.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>37</v>
       </c>
@@ -1337,7 +1659,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
@@ -1354,7 +1676,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
@@ -1371,7 +1693,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
@@ -1388,7 +1710,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
@@ -1405,7 +1727,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>19</v>
       </c>
@@ -1422,7 +1744,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
@@ -1439,7 +1761,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
@@ -1456,7 +1778,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>20</v>
       </c>
@@ -1473,7 +1795,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
@@ -1498,14 +1820,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E45573-BA0A-43D4-A9B6-5820F0234D40}">
   <dimension ref="B3:E27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -1519,7 +1841,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>16</v>
       </c>
@@ -1533,7 +1855,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>12.5</v>
       </c>
@@ -1547,7 +1869,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>10</v>
       </c>
@@ -1561,7 +1883,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>8</v>
       </c>
@@ -1575,7 +1897,7 @@
         <v>99.59</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>6.3</v>
       </c>
@@ -1589,7 +1911,7 @@
         <v>98.45</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>5</v>
       </c>
@@ -1603,7 +1925,7 @@
         <v>95.93</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>4</v>
       </c>
@@ -1617,7 +1939,7 @@
         <v>922.46</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>3.15</v>
       </c>
@@ -1631,7 +1953,7 @@
         <v>88.42</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>2.5</v>
       </c>
@@ -1645,7 +1967,7 @@
         <v>84.78</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>2</v>
       </c>
@@ -1659,7 +1981,7 @@
         <v>81.95</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>1.6</v>
       </c>
@@ -1673,7 +1995,7 @@
         <v>79.42</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>1.25</v>
       </c>
@@ -1687,7 +2009,7 @@
         <v>77.540000000000006</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>1</v>
       </c>
@@ -1701,7 +2023,7 @@
         <v>75.64</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>0.8</v>
       </c>
@@ -1715,7 +2037,7 @@
         <v>73.900000000000006</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>0.63</v>
       </c>
@@ -1729,7 +2051,7 @@
         <v>72.430000000000007</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>0.5</v>
       </c>
@@ -1743,7 +2065,7 @@
         <v>71.099999999999994</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>0.4</v>
       </c>
@@ -1757,7 +2079,7 @@
         <v>69.34</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>0.315</v>
       </c>
@@ -1771,7 +2093,7 @@
         <v>67.62</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>0.25</v>
       </c>
@@ -1785,7 +2107,7 @@
         <v>65.900000000000006</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>0.2</v>
       </c>
@@ -1799,7 +2121,7 @@
         <v>63.93</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>0.16</v>
       </c>
@@ -1813,7 +2135,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>0.125</v>
       </c>
@@ -1827,7 +2149,7 @@
         <v>60.122</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>0.1</v>
       </c>
@@ -1841,7 +2163,7 @@
         <v>58.18</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>0.08</v>
       </c>
@@ -1863,23 +2185,23 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E36B5748-34A6-400E-862B-00595A9697B8}">
   <dimension ref="A2:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -1894,7 +2216,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2">
         <v>7.0300000000000001E-2</v>
@@ -1909,7 +2231,7 @@
         <v>57.42</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>0.499</v>
@@ -1924,7 +2246,7 @@
         <v>57.32</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>3.5400000000000001E-2</v>
@@ -1939,7 +2261,7 @@
         <v>53.31</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>0.224</v>
@@ -1954,7 +2276,7 @@
         <v>51.49</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2">
         <v>1.5900000000000001E-2</v>
@@ -1969,7 +2291,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>51</v>
       </c>
@@ -1986,7 +2308,7 @@
         <v>41.14</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2">
         <v>8.0000000000000002E-3</v>
@@ -2001,7 +2323,7 @@
         <v>31.122</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2">
         <v>5.7000000000000002E-3</v>
@@ -2016,7 +2338,7 @@
         <v>224.75</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2">
         <v>3.3E-3</v>
@@ -2039,15 +2361,15 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42CFF1B4-FC42-4C68-A438-0038D97B52DC}">
   <dimension ref="B3:E29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -2061,7 +2383,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>25</v>
       </c>
@@ -2075,7 +2397,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>20</v>
       </c>
@@ -2089,7 +2411,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>16</v>
       </c>
@@ -2103,7 +2425,7 @@
         <v>99.72</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>12.5</v>
       </c>
@@ -2117,7 +2439,7 @@
         <v>98.87</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>10</v>
       </c>
@@ -2131,7 +2453,7 @@
         <v>95.05</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>8</v>
       </c>
@@ -2145,7 +2467,7 @@
         <v>90.63</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>6.3</v>
       </c>
@@ -2159,7 +2481,7 @@
         <v>94.22</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>5</v>
       </c>
@@ -2173,7 +2495,7 @@
         <v>76.349999999999994</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>4</v>
       </c>
@@ -2187,7 +2509,7 @@
         <v>69.38</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>3.15</v>
       </c>
@@ -2201,7 +2523,7 @@
         <v>63.84</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>2.5</v>
       </c>
@@ -2215,7 +2537,7 @@
         <v>59.15</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>2</v>
       </c>
@@ -2229,7 +2551,7 @@
         <v>56.09</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>1.6</v>
       </c>
@@ -2243,7 +2565,7 @@
         <v>52.56</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>1.25</v>
       </c>
@@ -2257,7 +2579,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>1</v>
       </c>
@@ -2271,7 +2593,7 @@
         <v>49.78</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>0.8</v>
       </c>
@@ -2285,7 +2607,7 @@
         <v>48.91</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>0.63</v>
       </c>
@@ -2299,7 +2621,7 @@
         <v>47.48</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>0.5</v>
       </c>
@@ -2313,7 +2635,7 @@
         <v>46.28</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>0.4</v>
       </c>
@@ -2327,7 +2649,7 @@
         <v>44.98</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>0.315</v>
       </c>
@@ -2341,7 +2663,7 @@
         <v>43.63</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>0.25</v>
       </c>
@@ -2355,7 +2677,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>0.2</v>
       </c>
@@ -2369,7 +2691,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>0.16</v>
       </c>
@@ -2383,7 +2705,7 @@
         <v>39.32</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>0.125</v>
       </c>
@@ -2397,7 +2719,7 @@
         <v>38.14</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>0.1</v>
       </c>
@@ -2411,7 +2733,7 @@
         <v>37.32</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>0.08</v>
       </c>
@@ -2433,15 +2755,15 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62F05E07-B36E-486A-B954-7993D95990F4}">
   <dimension ref="C4:F13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
@@ -2455,7 +2777,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C5" s="2">
         <v>6.6100000000000006E-2</v>
       </c>
@@ -2469,7 +2791,7 @@
         <v>34.08</v>
       </c>
     </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C6" s="2">
         <v>4.7100000000000003E-2</v>
       </c>
@@ -2483,7 +2805,7 @@
         <v>28.91</v>
       </c>
     </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C7" s="2">
         <v>3.3599999999999998E-2</v>
       </c>
@@ -2497,7 +2819,7 @@
         <v>24.76</v>
       </c>
     </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C8" s="2">
         <v>2.1499999999999998E-2</v>
       </c>
@@ -2511,7 +2833,7 @@
         <v>19.14</v>
       </c>
     </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C9" s="2">
         <v>1.26E-2</v>
       </c>
@@ -2525,7 +2847,7 @@
         <v>15.39</v>
       </c>
     </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C10" s="2">
         <v>7.3000000000000001E-3</v>
       </c>
@@ -2539,7 +2861,7 @@
         <v>13.97</v>
       </c>
     </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C11" s="2">
         <v>4.4999999999999997E-3</v>
       </c>
@@ -2553,7 +2875,7 @@
         <v>12.42</v>
       </c>
     </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C12" s="2">
         <v>2.7000000000000001E-3</v>
       </c>
@@ -2567,7 +2889,7 @@
         <v>11.01</v>
       </c>
     </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C13" s="2">
         <v>1.2999999999999999E-3</v>
       </c>
@@ -2589,15 +2911,15 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76A41ABA-1159-46B8-ACDE-10FD24ED54A3}">
   <dimension ref="B3:E27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -2611,7 +2933,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>16</v>
       </c>
@@ -2625,7 +2947,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>12.5</v>
       </c>
@@ -2639,7 +2961,7 @@
         <v>99.89</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>10</v>
       </c>
@@ -2653,7 +2975,7 @@
         <v>99.79</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>8</v>
       </c>
@@ -2667,7 +2989,7 @@
         <v>99.62</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>6.3</v>
       </c>
@@ -2681,7 +3003,7 @@
         <v>99.28</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>5</v>
       </c>
@@ -2695,7 +3017,7 @@
         <v>98.67</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>4</v>
       </c>
@@ -2709,7 +3031,7 @@
         <v>98.04</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>3.15</v>
       </c>
@@ -2723,7 +3045,7 @@
         <v>97.05</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>2.5</v>
       </c>
@@ -2737,7 +3059,7 @@
         <v>96.83</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>2</v>
       </c>
@@ -2751,7 +3073,7 @@
         <v>96.06</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>1.6</v>
       </c>
@@ -2765,7 +3087,7 @@
         <v>94.87</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>1.25</v>
       </c>
@@ -2779,7 +3101,7 @@
         <v>93.46</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>1</v>
       </c>
@@ -2793,7 +3115,7 @@
         <v>91.9</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>0.8</v>
       </c>
@@ -2807,7 +3129,7 @@
         <v>90.26</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>0.63</v>
       </c>
@@ -2821,7 +3143,7 @@
         <v>87.85</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>0.5</v>
       </c>
@@ -2835,7 +3157,7 @@
         <v>95.57</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>0.4</v>
       </c>
@@ -2849,7 +3171,7 @@
         <v>83.14</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>0.315</v>
       </c>
@@ -2863,7 +3185,7 @@
         <v>80.34</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>0.25</v>
       </c>
@@ -2877,7 +3199,7 @@
         <v>77.319999999999993</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>0.2</v>
       </c>
@@ -2891,7 +3213,7 @@
         <v>74.400000000000006</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>0.16</v>
       </c>
@@ -2905,7 +3227,7 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>0.125</v>
       </c>
@@ -2919,7 +3241,7 @@
         <v>70.36</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>0.1</v>
       </c>
@@ -2933,7 +3255,7 @@
         <v>67.47</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>0.08</v>
       </c>
@@ -2955,19 +3277,19 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2666205-3B58-48F3-B11D-09591713D617}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
@@ -2981,7 +3303,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>7.0199999999999999E-2</v>
       </c>
@@ -2989,7 +3311,7 @@
         <v>61.2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>0.05</v>
       </c>
@@ -2997,7 +3319,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>3.56E-2</v>
       </c>
@@ -3005,7 +3327,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2.29E-2</v>
       </c>
@@ -3013,7 +3335,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1.34E-2</v>
       </c>
@@ -3021,7 +3343,7 @@
         <v>28.74</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>7.7999999999999996E-3</v>
       </c>
@@ -3029,7 +3351,7 @@
         <v>19.02</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>4.7999999999999996E-3</v>
       </c>
@@ -3037,7 +3359,7 @@
         <v>13.42</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>2.8E-3</v>
       </c>
@@ -3045,7 +3367,7 @@
         <v>10.95</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1.4E-3</v>
       </c>
@@ -3061,15 +3383,15 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDBA4CAD-D6B4-468E-B37F-6E88FE652AC2}">
   <dimension ref="B3:E27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -3083,7 +3405,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>16</v>
       </c>
@@ -3097,7 +3419,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>12.5</v>
       </c>
@@ -3111,7 +3433,7 @@
         <v>99.92</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>10</v>
       </c>
@@ -3125,7 +3447,7 @@
         <v>99.92</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>8</v>
       </c>
@@ -3139,7 +3461,7 @@
         <v>99.78</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>6.3</v>
       </c>
@@ -3153,7 +3475,7 @@
         <v>99.46</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>5</v>
       </c>
@@ -3167,7 +3489,7 @@
         <v>98.99</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>4</v>
       </c>
@@ -3181,7 +3503,7 @@
         <v>98.55</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>3.15</v>
       </c>
@@ -3195,7 +3517,7 @@
         <v>98.08</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>2.5</v>
       </c>
@@ -3209,7 +3531,7 @@
         <v>97.24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>2</v>
       </c>
@@ -3223,7 +3545,7 @@
         <v>96.06</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>1.6</v>
       </c>
@@ -3237,7 +3559,7 @@
         <v>94.02</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>1.25</v>
       </c>
@@ -3251,7 +3573,7 @@
         <v>91.58</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>1</v>
       </c>
@@ -3265,7 +3587,7 @@
         <v>88.51</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>0.8</v>
       </c>
@@ -3279,7 +3601,7 @@
         <v>84.91</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>0.63</v>
       </c>
@@ -3293,7 +3615,7 @@
         <v>79.38</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>0.5</v>
       </c>
@@ -3307,7 +3629,7 @@
         <v>73.72</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>0.4</v>
       </c>
@@ -3321,7 +3643,7 @@
         <v>68.11</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>0.315</v>
       </c>
@@ -3335,7 +3657,7 @@
         <v>61.82</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>0.25</v>
       </c>
@@ -3349,7 +3671,7 @@
         <v>56.55</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>0.2</v>
       </c>
@@ -3363,7 +3685,7 @@
         <v>50.85</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>0.16</v>
       </c>
@@ -3377,7 +3699,7 @@
         <v>47.02</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>0.125</v>
       </c>
@@ -3391,7 +3713,7 @@
         <v>44.49</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>0.1</v>
       </c>
@@ -3405,7 +3727,7 @@
         <v>43.51</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>0.08</v>
       </c>
@@ -3427,15 +3749,15 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9043987E-5D60-4D57-9360-C8A38280CB97}">
   <dimension ref="B5:E14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
@@ -3449,7 +3771,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>7.1400000000000005E-2</v>
       </c>
@@ -3457,7 +3779,7 @@
         <v>39.799999999999997</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>5.0599999999999999E-2</v>
       </c>
@@ -3465,7 +3787,7 @@
         <v>36.19</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>3.6400000000000002E-2</v>
       </c>
@@ -3473,7 +3795,7 @@
         <v>27.41</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>2.3099999999999999E-2</v>
       </c>
@@ -3481,7 +3803,7 @@
         <v>23.17</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1.6299999999999999E-2</v>
       </c>
@@ -3489,7 +3811,7 @@
         <v>19.36</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1.15E-2</v>
       </c>
@@ -3497,7 +3819,7 @@
         <v>15.49</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>8.2000000000000007E-3</v>
       </c>
@@ -3505,7 +3827,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>5.7999999999999996E-3</v>
       </c>
@@ -3513,7 +3835,7 @@
         <v>13.51</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>3.3999999999999998E-3</v>
       </c>
@@ -3529,17 +3851,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB12E069-5C34-4DD7-A16E-2038C0A3E306}">
   <dimension ref="A3:F12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>5</v>
       </c>
@@ -3553,7 +3875,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C4">
         <v>7.1400000000000005E-2</v>
       </c>
@@ -3567,7 +3889,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C5">
         <v>5.0599999999999999E-2</v>
       </c>
@@ -3581,7 +3903,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C6">
         <v>3.6400000000000002E-2</v>
       </c>
@@ -3595,7 +3917,7 @@
         <v>12.32</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C7">
         <v>2.3099999999999999E-2</v>
       </c>
@@ -3609,7 +3931,7 @@
         <v>10.87</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -3629,7 +3951,7 @@
         <v>10.71</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C9">
         <v>1.15E-2</v>
       </c>
@@ -3643,7 +3965,7 @@
         <v>10.63</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C10">
         <v>8.2199999999999999E-3</v>
       </c>
@@ -3657,7 +3979,7 @@
         <v>10.54</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C11">
         <v>5.7999999999999996E-3</v>
       </c>
@@ -3671,7 +3993,7 @@
         <v>10.38</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C12">
         <v>3.3999999999999998E-3</v>
       </c>
@@ -3693,15 +4015,15 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C974F8C-71C8-43E1-AD1A-8EA97D49CF11}">
   <dimension ref="B3:E29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -3715,7 +4037,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>25</v>
       </c>
@@ -3729,7 +4051,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>20</v>
       </c>
@@ -3743,7 +4065,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>16</v>
       </c>
@@ -3757,7 +4079,7 @@
         <v>99.47</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>12.5</v>
       </c>
@@ -3771,7 +4093,7 @@
         <v>99.1</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>10</v>
       </c>
@@ -3785,7 +4107,7 @@
         <v>98.07</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>8</v>
       </c>
@@ -3799,7 +4121,7 @@
         <v>97.25</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>6.3</v>
       </c>
@@ -3813,7 +4135,7 @@
         <v>94.48</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>5</v>
       </c>
@@ -3827,7 +4149,7 @@
         <v>90.23</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>4</v>
       </c>
@@ -3841,7 +4163,7 @@
         <v>86.15</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>3.15</v>
       </c>
@@ -3855,7 +4177,7 @@
         <v>81.63</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>2.5</v>
       </c>
@@ -3869,7 +4191,7 @@
         <v>76.52</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>2</v>
       </c>
@@ -3883,7 +4205,7 @@
         <v>72.89</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>1.6</v>
       </c>
@@ -3897,7 +4219,7 @@
         <v>69.22</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>1.25</v>
       </c>
@@ -3911,7 +4233,7 @@
         <v>66.650000000000006</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>1</v>
       </c>
@@ -3925,7 +4247,7 @@
         <v>63.2</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>0.8</v>
       </c>
@@ -3939,7 +4261,7 @@
         <v>59.78</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>0.63</v>
       </c>
@@ -3953,7 +4275,7 @@
         <v>54.6</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>0.5</v>
       </c>
@@ -3967,7 +4289,7 @@
         <v>50.33</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>0.4</v>
       </c>
@@ -3981,7 +4303,7 @@
         <v>46.6</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>0.315</v>
       </c>
@@ -3995,7 +4317,7 @@
         <v>42.43</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>0.25</v>
       </c>
@@ -4009,7 +4331,7 @@
         <v>39.15</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>0.2</v>
       </c>
@@ -4023,7 +4345,7 @@
         <v>34.450000000000003</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>0.16</v>
       </c>
@@ -4037,7 +4359,7 @@
         <v>30.27</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>0.125</v>
       </c>
@@ -4051,7 +4373,7 @@
         <v>27.88</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>0.1</v>
       </c>
@@ -4065,7 +4387,7 @@
         <v>26.56</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>0.08</v>
       </c>
@@ -4087,17 +4409,17 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68131514-12E3-48DB-9AEC-2569B1533413}">
   <dimension ref="A3:F12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
@@ -4111,7 +4433,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C4">
         <v>7.0300000000000001E-2</v>
       </c>
@@ -4119,7 +4441,7 @@
         <v>22.54</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C5">
         <v>4.99E-2</v>
       </c>
@@ -4127,7 +4449,7 @@
         <v>18.95</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C6">
         <v>3.5400000000000001E-2</v>
       </c>
@@ -4135,7 +4457,7 @@
         <v>16.11</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C7">
         <v>2.24E-2</v>
       </c>
@@ -4143,7 +4465,7 @@
         <v>13.48</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -4154,7 +4476,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C9">
         <v>1.1299999999999999E-2</v>
       </c>
@@ -4162,7 +4484,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C10">
         <v>8.0000000000000002E-3</v>
       </c>
@@ -4170,7 +4492,7 @@
         <v>12.45</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C11">
         <v>5.7000000000000002E-3</v>
       </c>
@@ -4178,7 +4500,7 @@
         <v>11.75</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C12">
         <v>3.3E-3</v>
       </c>
@@ -4194,20 +4516,20 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE7975A4-0339-41AE-A0E9-52B60A536860}">
   <dimension ref="A2:E27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -4221,7 +4543,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>16</v>
       </c>
@@ -4235,7 +4557,7 @@
         <v>99.47</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>12.5</v>
       </c>
@@ -4249,7 +4571,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>10</v>
       </c>
@@ -4263,7 +4585,7 @@
         <v>99.33</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>8</v>
       </c>
@@ -4277,7 +4599,7 @@
         <v>98.09</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>6.3</v>
       </c>
@@ -4291,7 +4613,7 @@
         <v>96.85</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>5</v>
       </c>
@@ -4305,7 +4627,7 @@
         <v>91.58</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>4</v>
       </c>
@@ -4319,7 +4641,7 @@
         <v>74.010000000000005</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>3.15</v>
       </c>
@@ -4333,7 +4655,7 @@
         <v>65.58</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>2.5</v>
       </c>
@@ -4347,7 +4669,7 @@
         <v>57.61</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>2</v>
       </c>
@@ -4361,7 +4683,7 @@
         <v>49.53</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>1.6</v>
       </c>
@@ -4375,7 +4697,7 @@
         <v>45.74</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>1.25</v>
       </c>
@@ -4389,7 +4711,7 @@
         <v>43.65</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>1</v>
       </c>
@@ -4403,7 +4725,7 @@
         <v>41.93</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>0.8</v>
       </c>
@@ -4417,7 +4739,7 @@
         <v>40.08</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>0.63</v>
       </c>
@@ -4431,7 +4753,7 @@
         <v>38.270000000000003</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>0.5</v>
       </c>
@@ -4445,7 +4767,7 @@
         <v>36.200000000000003</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>0.4</v>
       </c>
@@ -4459,7 +4781,7 @@
         <v>31.89</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>0.315</v>
       </c>
@@ -4473,7 +4795,7 @@
         <v>29.81</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>0.25</v>
       </c>
@@ -4487,7 +4809,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>0.2</v>
       </c>
@@ -4501,7 +4823,7 @@
         <v>26.47</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>0.16</v>
       </c>
@@ -4515,7 +4837,7 @@
         <v>24.92</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>0.125</v>
       </c>
@@ -4529,7 +4851,7 @@
         <v>24.33</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>0.1</v>
       </c>
@@ -4543,7 +4865,7 @@
         <v>24.08</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>0.08</v>
       </c>
@@ -4565,15 +4887,15 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B50F76E1-ED08-4493-9018-E0DBC17023DE}">
   <dimension ref="B3:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -4587,7 +4909,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>6.7699999999999996E-2</v>
       </c>
@@ -4595,7 +4917,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>4.82E-2</v>
       </c>
@@ -4603,7 +4925,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>3.4200000000000001E-2</v>
       </c>
@@ -4611,7 +4933,7 @@
         <v>12.32</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>2.1600000000000001E-2</v>
       </c>
@@ -4619,7 +4941,7 @@
         <v>10.87</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1.5299999999999999E-2</v>
       </c>
@@ -4627,7 +4949,7 @@
         <v>10.71</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1.0800000000000001E-2</v>
       </c>
@@ -4635,7 +4957,7 @@
         <v>10.63</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>7.6E-3</v>
       </c>
@@ -4643,7 +4965,7 @@
         <v>10.54</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>5.4000000000000003E-3</v>
       </c>
@@ -4651,7 +4973,7 @@
         <v>10.38</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>3.0999999999999999E-3</v>
       </c>
@@ -4666,9 +4988,468 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A11CF5D5-57EF-4F4E-ADF9-F099EC9BAD73}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="N3:Q36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="14" max="14" width="43.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N3" t="s">
+        <v>56</v>
+      </c>
+      <c r="O3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P3" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N5">
+        <v>10</v>
+      </c>
+      <c r="O5" t="s">
+        <v>61</v>
+      </c>
+      <c r="P5" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N6">
+        <v>8</v>
+      </c>
+      <c r="O6" t="s">
+        <v>63</v>
+      </c>
+      <c r="P6" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N7" t="s">
+        <v>66</v>
+      </c>
+      <c r="O7" t="s">
+        <v>67</v>
+      </c>
+      <c r="P7" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N8">
+        <v>5</v>
+      </c>
+      <c r="O8" t="s">
+        <v>70</v>
+      </c>
+      <c r="P8" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N9">
+        <v>4</v>
+      </c>
+      <c r="O9" t="s">
+        <v>73</v>
+      </c>
+      <c r="P9" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N10" t="s">
+        <v>76</v>
+      </c>
+      <c r="O10" t="s">
+        <v>77</v>
+      </c>
+      <c r="P10" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N11" t="s">
+        <v>80</v>
+      </c>
+      <c r="O11" t="s">
+        <v>81</v>
+      </c>
+      <c r="P11" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12" t="s">
+        <v>84</v>
+      </c>
+      <c r="P12" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N13" t="s">
+        <v>87</v>
+      </c>
+      <c r="O13" t="s">
+        <v>88</v>
+      </c>
+      <c r="P13" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N14" t="s">
+        <v>91</v>
+      </c>
+      <c r="O14" t="s">
+        <v>92</v>
+      </c>
+      <c r="P14" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15" t="s">
+        <v>95</v>
+      </c>
+      <c r="P15" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N16" t="s">
+        <v>98</v>
+      </c>
+      <c r="O16" t="s">
+        <v>99</v>
+      </c>
+      <c r="P16" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N17" t="s">
+        <v>102</v>
+      </c>
+      <c r="O17" t="s">
+        <v>103</v>
+      </c>
+      <c r="P17" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N18" t="s">
+        <v>106</v>
+      </c>
+      <c r="O18" t="s">
+        <v>107</v>
+      </c>
+      <c r="P18" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N19" t="s">
+        <v>110</v>
+      </c>
+      <c r="O19" t="s">
+        <v>111</v>
+      </c>
+      <c r="P19" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N20" t="s">
+        <v>114</v>
+      </c>
+      <c r="O20" t="s">
+        <v>115</v>
+      </c>
+      <c r="P20" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N21" t="s">
+        <v>118</v>
+      </c>
+      <c r="O21" t="s">
+        <v>119</v>
+      </c>
+      <c r="P21" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N22" t="s">
+        <v>122</v>
+      </c>
+      <c r="O22" t="s">
+        <v>123</v>
+      </c>
+      <c r="P22" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N23" t="s">
+        <v>126</v>
+      </c>
+      <c r="O23" t="s">
+        <v>127</v>
+      </c>
+      <c r="P23" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N24" t="s">
+        <v>130</v>
+      </c>
+      <c r="O24" t="s">
+        <v>131</v>
+      </c>
+      <c r="P24" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N25" t="s">
+        <v>134</v>
+      </c>
+      <c r="O25" t="s">
+        <v>135</v>
+      </c>
+      <c r="P25" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N26" t="s">
+        <v>138</v>
+      </c>
+      <c r="O26" t="s">
+        <v>139</v>
+      </c>
+      <c r="P26" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N27" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N28" t="s">
+        <v>143</v>
+      </c>
+      <c r="O28" t="s">
+        <v>52</v>
+      </c>
+      <c r="P28" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N29" t="s">
+        <v>145</v>
+      </c>
+      <c r="O29" t="s">
+        <v>52</v>
+      </c>
+      <c r="P29" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N30" t="s">
+        <v>147</v>
+      </c>
+      <c r="O30" t="s">
+        <v>52</v>
+      </c>
+      <c r="P30" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="31" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N31" t="s">
+        <v>149</v>
+      </c>
+      <c r="O31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N32" t="s">
+        <v>151</v>
+      </c>
+      <c r="O32" t="s">
+        <v>52</v>
+      </c>
+      <c r="P32" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N33" t="s">
+        <v>153</v>
+      </c>
+      <c r="O33" t="s">
+        <v>52</v>
+      </c>
+      <c r="P33" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="34" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N34" t="s">
+        <v>155</v>
+      </c>
+      <c r="O34" t="s">
+        <v>52</v>
+      </c>
+      <c r="P34" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="35" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N35" t="s">
+        <v>157</v>
+      </c>
+      <c r="O35" t="s">
+        <v>52</v>
+      </c>
+      <c r="P35" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="36" spans="14:17" x14ac:dyDescent="0.25">
+      <c r="N36" t="s">
+        <v>159</v>
+      </c>
+      <c r="O36" t="s">
+        <v>52</v>
+      </c>
+      <c r="P36" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4676,7 +5457,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6DC5C43-595F-4794-8F46-C4BA39D94B87}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4685,7 +5466,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791E43AB-E2CE-4014-AEC3-B580998B3A0F}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4694,7 +5475,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5727BC25-096E-4A9B-B48B-55BFA73278E3}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4703,7 +5484,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C5CDB2F-E8F2-445C-80FC-567A7E3C44ED}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4712,7 +5493,7 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{278E7301-528F-4F97-AF00-67B207422C24}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4721,16 +5502,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBC469C3-A214-422D-A00B-1DA4F9BE1620}">
   <dimension ref="B3:F29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>5</v>
       </c>
@@ -4744,7 +5525,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C4">
         <v>25</v>
       </c>
@@ -4758,7 +5539,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C5">
         <v>20</v>
       </c>
@@ -4772,7 +5553,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C6">
         <v>100</v>
       </c>
@@ -4786,7 +5567,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C7">
         <v>12.5</v>
       </c>
@@ -4800,7 +5581,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C8">
         <v>10</v>
       </c>
@@ -4814,7 +5595,7 @@
         <v>99.87</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C9">
         <v>8</v>
       </c>
@@ -4828,7 +5609,7 @@
         <v>99.66</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C10">
         <v>6.3</v>
       </c>
@@ -4842,7 +5623,7 @@
         <v>99.47</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>7</v>
       </c>
@@ -4859,7 +5640,7 @@
         <v>99.28</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C12">
         <v>4</v>
       </c>
@@ -4873,7 +5654,7 @@
         <v>98.92</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C13">
         <v>3.15</v>
       </c>
@@ -4887,7 +5668,7 @@
         <v>97.94</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C14">
         <v>2.5</v>
       </c>
@@ -4901,7 +5682,7 @@
         <v>96.97</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C15">
         <v>2</v>
       </c>
@@ -4915,7 +5696,7 @@
         <v>95.21</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C16">
         <v>1.6</v>
       </c>
@@ -4929,7 +5710,7 @@
         <v>92.34</v>
       </c>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C17">
         <v>1.25</v>
       </c>
@@ -4943,7 +5724,7 @@
         <v>88.85</v>
       </c>
     </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C18">
         <v>1</v>
       </c>
@@ -4957,7 +5738,7 @@
         <v>84.42</v>
       </c>
     </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C19">
         <v>0.8</v>
       </c>
@@ -4971,7 +5752,7 @@
         <v>80.290000000000006</v>
       </c>
     </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20">
         <v>0.63</v>
       </c>
@@ -4985,7 +5766,7 @@
         <v>74.849999999999994</v>
       </c>
     </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21">
         <v>0.5</v>
       </c>
@@ -4999,7 +5780,7 @@
         <v>69.91</v>
       </c>
     </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22">
         <v>0.4</v>
       </c>
@@ -5013,7 +5794,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C23">
         <v>0.315</v>
       </c>
@@ -5027,7 +5808,7 @@
         <v>61.72</v>
       </c>
     </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C24">
         <v>0.25</v>
       </c>
@@ -5041,7 +5822,7 @@
         <v>57.93</v>
       </c>
     </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C25">
         <v>0.2</v>
       </c>
@@ -5055,7 +5836,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C26">
         <v>0.16</v>
       </c>
@@ -5069,7 +5850,7 @@
         <v>47.81</v>
       </c>
     </row>
-    <row r="27" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C27">
         <v>0.125</v>
       </c>
@@ -5083,7 +5864,7 @@
         <v>45.58</v>
       </c>
     </row>
-    <row r="28" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C28">
         <v>0.1</v>
       </c>
@@ -5097,7 +5878,7 @@
         <v>44.46</v>
       </c>
     </row>
-    <row r="29" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C29">
         <v>0.08</v>
       </c>
@@ -5119,7 +5900,7 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCEC1E6-5215-4CC8-9926-B3436CFE7A2C}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5128,15 +5909,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8A457D-E7AE-44CB-A9CA-6BB005D37734}">
   <dimension ref="A4:E13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -5150,7 +5931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>6.7100000000000007E-2</v>
       </c>
@@ -5164,7 +5945,7 @@
         <v>40.130000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>4.7399999999999998E-2</v>
       </c>
@@ -5178,7 +5959,7 @@
         <v>32.47</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -5195,7 +5976,7 @@
         <v>28.22</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>2.1100000000000001E-2</v>
       </c>
@@ -5209,7 +5990,7 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -5223,7 +6004,7 @@
         <v>16.68</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1.0500000000000001E-2</v>
       </c>
@@ -5237,7 +6018,7 @@
         <v>16.14</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>7.7000000000000002E-3</v>
       </c>
@@ -5251,7 +6032,7 @@
         <v>15.06</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>5.4999999999999997E-3</v>
       </c>
@@ -5265,7 +6046,7 @@
         <v>15.07</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>3.2000000000000002E-3</v>
       </c>
@@ -5287,16 +6068,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BB40F73-0097-41C1-AF19-14D68A7BA2CE}">
   <dimension ref="A3:E29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -5310,7 +6091,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>25</v>
       </c>
@@ -5324,7 +6105,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>20</v>
       </c>
@@ -5338,7 +6119,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>100</v>
       </c>
@@ -5352,7 +6133,7 @@
         <v>99.72</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>12.5</v>
       </c>
@@ -5366,7 +6147,7 @@
         <v>98.87</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>10</v>
       </c>
@@ -5380,7 +6161,7 @@
         <v>95.05</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>8</v>
       </c>
@@ -5394,7 +6175,7 @@
         <v>90.63</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>6.3</v>
       </c>
@@ -5408,7 +6189,7 @@
         <v>84.22</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>5</v>
       </c>
@@ -5422,7 +6203,7 @@
         <v>76.349999999999994</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -5439,7 +6220,7 @@
         <v>69.38</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>3.15</v>
       </c>
@@ -5453,7 +6234,7 @@
         <v>63.84</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>2.5</v>
       </c>
@@ -5467,7 +6248,7 @@
         <v>59.15</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>2</v>
       </c>
@@ -5481,7 +6262,7 @@
         <v>56.15</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>1.6</v>
       </c>
@@ -5495,7 +6276,7 @@
         <v>53.56</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>1.25</v>
       </c>
@@ -5509,7 +6290,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>1</v>
       </c>
@@ -5523,7 +6304,7 @@
         <v>49.78</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>0.8</v>
       </c>
@@ -5537,7 +6318,7 @@
         <v>48.91</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>0.63</v>
       </c>
@@ -5551,7 +6332,7 @@
         <v>47.48</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>0.5</v>
       </c>
@@ -5565,7 +6346,7 @@
         <v>46.28</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>0.4</v>
       </c>
@@ -5579,7 +6360,7 @@
         <v>44.98</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>0.315</v>
       </c>
@@ -5593,7 +6374,7 @@
         <v>43.63</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>0.25</v>
       </c>
@@ -5607,7 +6388,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>0.2</v>
       </c>
@@ -5621,7 +6402,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>0.16</v>
       </c>
@@ -5635,7 +6416,7 @@
         <v>39.32</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>0.125</v>
       </c>
@@ -5649,7 +6430,7 @@
         <v>38.14</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>0.1</v>
       </c>
@@ -5663,7 +6444,7 @@
         <v>37.32</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>0.08</v>
       </c>
@@ -5685,17 +6466,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3DAB236-924C-4C3A-B0E2-25F3686D2857}">
   <dimension ref="B3:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.33203125" customWidth="1"/>
-    <col min="4" max="4" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.28515625" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
         <v>5</v>
       </c>
@@ -5709,7 +6490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D4">
         <v>7.0199999999999999E-2</v>
       </c>
@@ -5723,7 +6504,7 @@
         <v>34.08</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D5">
         <v>0.05</v>
       </c>
@@ -5737,7 +6518,7 @@
         <v>28.91</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>10</v>
       </c>
@@ -5754,7 +6535,7 @@
         <v>24.91</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D7">
         <v>0.22900000000000001</v>
       </c>
@@ -5768,7 +6549,7 @@
         <v>19.14</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D8">
         <v>1.34E-2</v>
       </c>
@@ -5782,7 +6563,7 @@
         <v>15.39</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D9">
         <v>7.7999999999999996E-3</v>
       </c>
@@ -5796,7 +6577,7 @@
         <v>13.97</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D10">
         <v>4.7999999999999996E-3</v>
       </c>
@@ -5810,7 +6591,7 @@
         <v>12.42</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D11">
         <v>2.8E-3</v>
       </c>
@@ -5824,7 +6605,7 @@
         <v>11.01</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D12">
         <v>1.4E-3</v>
       </c>
@@ -5846,15 +6627,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47548A7F-F51A-470F-80A2-008514A0D802}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="39.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -5862,7 +6643,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>13</v>
       </c>
@@ -5879,7 +6660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C4">
         <v>1</v>
       </c>
@@ -5896,7 +6677,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C5">
         <v>1</v>
       </c>
@@ -5913,7 +6694,7 @@
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C6">
         <v>1</v>
       </c>
@@ -5930,7 +6711,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C7">
         <v>2</v>
       </c>
@@ -5947,7 +6728,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C8">
         <v>2</v>
       </c>
@@ -5964,7 +6745,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C9">
         <v>2</v>
       </c>
@@ -5981,7 +6762,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C10">
         <v>3</v>
       </c>
@@ -5998,7 +6779,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C11">
         <v>3</v>
       </c>
@@ -6015,7 +6796,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C12">
         <v>3</v>
       </c>
@@ -6040,19 +6821,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AF142DA-CEB8-4764-B6D4-0BEA75BDCE0C}">
   <dimension ref="A1:G15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>13</v>
       </c>
@@ -6072,7 +6853,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1</v>
       </c>
@@ -6092,7 +6873,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
@@ -6112,7 +6893,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1</v>
       </c>
@@ -6132,7 +6913,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1</v>
       </c>
@@ -6152,7 +6933,7 @@
         <v>28.66</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>2</v>
       </c>
@@ -6172,7 +6953,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>2</v>
       </c>
@@ -6192,7 +6973,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>2</v>
       </c>
@@ -6212,7 +6993,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>2</v>
       </c>
@@ -6232,7 +7013,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>3</v>
       </c>
@@ -6252,7 +7033,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>3</v>
       </c>
@@ -6272,7 +7053,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>3</v>
       </c>
@@ -6292,7 +7073,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>3</v>
       </c>
@@ -6320,19 +7101,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E98A1F4-0DB4-477C-835A-F95E410296AB}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>13</v>
       </c>
@@ -6349,7 +7130,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1</v>
       </c>
@@ -6366,7 +7147,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
@@ -6383,7 +7164,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1</v>
       </c>
@@ -6400,7 +7181,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1</v>
       </c>
@@ -6417,7 +7198,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>2</v>
       </c>
@@ -6434,7 +7215,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>2</v>
       </c>
@@ -6451,7 +7232,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>2</v>
       </c>
@@ -6468,7 +7249,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>2</v>
       </c>
@@ -6485,7 +7266,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>3</v>
       </c>
@@ -6502,7 +7283,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>3</v>
       </c>
@@ -6519,7 +7300,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>3</v>
       </c>
@@ -6536,7 +7317,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>3</v>
       </c>
